--- a/426-config---paramètre-pin-all/ig/StructureDefinition-tddui-comment.xlsx
+++ b/426-config---paramètre-pin-all/ig/StructureDefinition-tddui-comment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T15:49:47+00:00</t>
+    <t>2026-01-30T16:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
   </si>
   <si>
     <t>Abstract</t>
